--- a/public/SEOFlow-77-Platform-Campaign-Report.xlsx
+++ b/public/SEOFlow-77-Platform-Campaign-Report.xlsx
@@ -923,7 +923,7 @@
     <t>VERIFIED_SUCCESS: профиль создан и публично доступен (18+ млн бизнесов в каталоге)</t>
   </si>
   <si>
-    <t>VERIFIED_SUCCESS: Профиль создан и публично доступен. URL: https://www.find-us-here.com/businesses/Itllect-LLC-Plantation-Florida-USA/34578398/. Аккаунт: itllect / DimaItllect2026!55. Заполнены: контакты, адрес, категория (Advertising - Direct Mail), описание. Email verification не требуется (аккаунт активирован сразу).</t>
+    <t>VERIFIED_SUCCESS: Профиль создан и публично доступен. URL: https://www.find-us-here.com/businesses/Itllect-LLC-Plantation-Florida-USA/34578398/. Аккаунт: itllect / [REDACTED]. Заполнены: контакты, адрес, категория (Advertising - Direct Mail), описание. Email verification не требуется (аккаунт активирован сразу).</t>
   </si>
   <si>
     <t>Подтверждено в headed-сессии 31.07 (turnstile решён, submit прошёл)</t>
@@ -968,7 +968,7 @@
     <t>VERIFIED_SUCCESS: профиль создан и публично доступен</t>
   </si>
   <si>
-    <t>VERIFIED_SUCCESS: Профиль создан и подтверждён. URL: https://www.semfirms.com/profile/itllect-llc. Аккаунт: itllect.marketing@gmail.com / DimaItllect2026!55. Блокировало: поле title требовало 'Itllect LLC' (полное юридическое название). Drupal валидация отклоняла форму без полного названия компании.</t>
+    <t>VERIFIED_SUCCESS: Профиль создан и подтверждён. URL: https://www.semfirms.com/profile/itllect-llc. Аккаунт: itllect.marketing@gmail.com / [REDACTED]. Блокировало: поле title требовало 'Itllect LLC' (полное юридическое название). Drupal валидация отклоняла форму без полного названия компании.</t>
   </si>
   <si>
     <t>Форма жива на /registration (Drupal); заполнение проходит, submit зависает — нужен ручной шаг</t>
@@ -1058,7 +1058,7 @@
     <t>BLOCKED: Cloudflare 403 — 'Sorry, you have been blocked' (headed + headless, 11.08); no login session, no saved credentials, OAuth-only per docs</t>
   </si>
   <si>
-    <t>VERIFIED_SUCCESS: company profile создан и публично доступен — https://wellfound.com/company/itllect (slug itllect, location Coral Springs, Software, 1-10, Founder: Dmitrii Dovzhenko). Регистрация аккаунта itllect.marketing@gmail.com + профиль заполнены в headed-сессии 11.08; step 1 onboarding завершён, invite-шаг пропущен.</t>
+    <t>VERIFIED_SUCCESS: company profile создан и публично доступен — https://wellfound.com/company/itllect (slug itllect, location Coral Springs, Software, 1-10, Founder: [REDACTED]). Регистрация аккаунта itllect.marketing@gmail.com + профиль заполнены в headed-сессии 11.08; step 1 onboarding завершён, invite-шаг пропущен.</t>
   </si>
   <si>
     <t>Real success verified via live public profile URL + onboarding progress (green check on Set up your account). Replaces earlier FALSE POSITIVE SUBMITTED (404 on /companies/new).</t>
@@ -1588,7 +1588,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -4107,7 +4107,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -4533,7 +4533,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -4956,7 +4956,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -6770,6 +6770,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>